--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>test1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -484,33 +484,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>test2</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>500</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -524,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,55 +541,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amit Patil</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-16 12:51:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OUT</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Suresh Kumar</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-04-16 13:00:29</t>
+          <t>2026-04-16 15:16:00</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,6 +485,32 @@
       </c>
       <c r="F2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>filter</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D3" t="n">
+        <v>900</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineers" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,19 +465,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test1</t>
+          <t>xsy</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
+        <v>4000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -484,33 +485,215 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>200</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>filter</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>250</v>
-      </c>
-      <c r="D3" t="n">
-        <v>900</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>valve</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>600</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>OG</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="F4" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>300</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>700</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5700</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dis</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test 8</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="n">
+        <v>90</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>400</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -524,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,25 +718,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Sr_No</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Purchase_Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tax_Invoice_No</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Charges</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>In_Date</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Out_Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -562,30 +765,5536 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:33:50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:33:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:33:58</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:33:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:34:05</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:34:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:16:50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sham Kachi</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:17:14</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:17:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:02:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:29:07</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:29:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sahil Dighe</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:30:54</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:30:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:30:29</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:30:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:31:13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:31:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:08:57</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:07:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>21</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TI-123</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:28:54</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:28:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>22</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TI-123</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:29:02</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:29:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Nagendra Yadav</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:34:48</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:34:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>9</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>11</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>12</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>13</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>14</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>16</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>17</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>18</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>19</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>21</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>22</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>23</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>24</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>25</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>26</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>27</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>28</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>29</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>30</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>31</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>32</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>33</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>34</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>35</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>36</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>37</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>38</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>39</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>40</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:33:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Abhitabh Gupta</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>300</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:54:08</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>8</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:43:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>400</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:49</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>kishor panchal</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>400</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:36</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>7</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Faruk Shaikh</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>400</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:07</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:52:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>9</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>10</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>vss105</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-04-17 11:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>3</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>6</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>7</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>8</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>10</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>11</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>12</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lalemashak kunnure</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:46:22</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:46:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:19:55</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:19:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>6</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>7</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>8</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>9</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>10</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>11</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>12</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>13</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>14</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>15</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>vss109</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:18:53</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Engineer_Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>BP_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PPRR_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Created_At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Store</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-04-16 15:16:00</t>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sham Kachi</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sameer shaikh</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rajesh chavan</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sahil Dighe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>kishor panchal</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Raju Yadav</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lalemashak kunnure</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Faruk Shaikh</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ashraf Momin</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Abhitabh Gupta</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Prahalad Yadav</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Abdul Rehman</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ishwar Panchal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nagendra Yadav</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Pramod Valekar</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Rahim Dindore</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:47:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-04-17 12:48:07</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Service_Billing" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,12 +32,24 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -57,11 +70,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +502,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -776,7 +793,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -820,7 +836,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -864,7 +879,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -908,7 +922,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>IN</t>
@@ -927,7 +940,6 @@
           <t>2026-04-17 11:02:12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2026-04-17 11:02:12</t>
@@ -948,7 +960,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -962,7 +973,6 @@
       <c r="G6" t="n">
         <v>4000</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>2026-04-17 11:16:50</t>
@@ -988,29 +998,32 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>vishal</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>2026-04-17 11:02:12</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:11:39</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-18 17:11:39</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1041,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1047,7 +1059,6 @@
           <t>2026-04-17 11:02:12</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2026-04-17 11:02:12</t>
@@ -1068,7 +1079,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1087,7 +1097,6 @@
           <t>2026-04-17 11:02:12</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2026-04-17 11:02:12</t>
@@ -1108,7 +1117,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1122,7 +1130,6 @@
       <c r="G10" t="n">
         <v>4000</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>2026-04-17 11:17:14</t>
@@ -1148,7 +1155,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1167,7 +1173,6 @@
           <t>2026-04-17 11:02:12</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2026-04-17 11:02:12</t>
@@ -1188,7 +1193,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1202,7 +1206,6 @@
       <c r="G12" t="n">
         <v>1000</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2026-04-17 11:29:07</t>
@@ -1228,7 +1231,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1242,7 +1244,6 @@
       <c r="G13" t="n">
         <v>1000</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2026-04-17 11:30:54</t>
@@ -1268,7 +1269,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1287,7 +1287,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1308,7 +1307,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1322,7 +1320,6 @@
       <c r="G15" t="n">
         <v>1000</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2026-04-17 11:30:29</t>
@@ -1348,7 +1345,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1362,7 +1358,6 @@
       <c r="G16" t="n">
         <v>1000</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2026-04-17 11:31:13</t>
@@ -1388,7 +1383,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1407,7 +1401,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1428,7 +1421,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1447,7 +1439,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1468,7 +1459,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1487,7 +1477,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1508,7 +1497,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1527,7 +1515,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1548,7 +1535,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1567,7 +1553,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1588,7 +1573,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1607,7 +1591,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1628,7 +1611,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1647,7 +1629,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1668,7 +1649,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1687,7 +1667,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1708,7 +1687,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1727,7 +1705,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1748,7 +1725,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1767,7 +1743,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1788,7 +1763,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1807,7 +1781,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1828,7 +1801,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1847,7 +1819,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1868,7 +1839,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>OUT</t>
@@ -1882,7 +1852,6 @@
       <c r="G29" t="n">
         <v>1000</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2026-04-17 11:08:57</t>
@@ -1908,7 +1877,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1927,7 +1895,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -1948,7 +1915,6 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>IN</t>
@@ -1967,7 +1933,6 @@
           <t>2026-04-17 11:07:54</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2026-04-17 11:07:54</t>
@@ -2011,7 +1976,6 @@
           <t>2026-04-17 11:28:54</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2026-04-17 11:28:54</t>
@@ -2055,7 +2019,6 @@
           <t>2026-04-17 11:29:02</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2026-04-17 11:29:02</t>
@@ -2094,7 +2057,6 @@
       <c r="G34" t="n">
         <v>6000</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2026-04-17 11:34:48</t>
@@ -2143,7 +2105,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2187,7 +2148,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2231,7 +2191,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2275,7 +2234,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2319,7 +2277,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2363,7 +2320,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2407,7 +2363,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2451,7 +2406,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2495,7 +2449,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2539,7 +2492,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2583,7 +2535,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2627,7 +2578,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2671,7 +2621,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2715,7 +2664,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2759,7 +2707,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2803,7 +2750,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2847,7 +2793,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2891,7 +2836,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2935,7 +2879,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -2979,7 +2922,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3023,7 +2965,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3067,7 +3008,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3111,7 +3051,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3155,7 +3094,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3199,7 +3137,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3243,7 +3180,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3287,7 +3223,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3331,7 +3266,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3375,7 +3309,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3419,7 +3352,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3463,7 +3395,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3507,7 +3438,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3551,7 +3481,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3595,7 +3524,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3639,7 +3567,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3683,7 +3610,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3727,7 +3653,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3771,7 +3696,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3815,7 +3739,6 @@
           <t>2026-04-17 11:33:16</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>2026-04-17 11:33:16</t>
@@ -3854,7 +3777,6 @@
       <c r="G74" t="n">
         <v>300</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2026-04-17 11:54:08</t>
@@ -3903,7 +3825,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -3947,7 +3868,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -3991,7 +3911,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4035,7 +3954,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4079,7 +3997,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4123,7 +4040,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4167,7 +4083,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4211,7 +4126,6 @@
           <t>2026-04-17 11:43:33</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>2026-04-17 11:43:33</t>
@@ -4250,7 +4164,6 @@
       <c r="G83" t="n">
         <v>400</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2026-04-17 11:52:49</t>
@@ -4299,7 +4212,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4343,7 +4255,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4382,7 +4293,6 @@
       <c r="G86" t="n">
         <v>400</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2026-04-17 11:52:36</t>
@@ -4431,7 +4341,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4475,7 +4384,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4514,7 +4422,6 @@
       <c r="G89" t="n">
         <v>400</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2026-04-17 11:52:07</t>
@@ -4563,7 +4470,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4607,7 +4513,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4651,7 +4556,6 @@
           <t>2026-04-17 11:51:08</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
           <t>2026-04-17 11:51:08</t>
@@ -4695,7 +4599,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4739,7 +4642,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4783,7 +4685,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4827,7 +4728,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4871,7 +4771,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4915,7 +4814,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -4959,7 +4857,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5003,7 +4900,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5047,7 +4943,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5091,7 +4986,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5135,7 +5029,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5179,7 +5072,6 @@
           <t>2026-04-17 12:13:30</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>2026-04-17 12:13:30</t>
@@ -5223,7 +5115,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5310,7 +5201,6 @@
       <c r="G107" t="n">
         <v>3500</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2026-04-17 12:19:55</t>
@@ -5359,7 +5249,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5403,7 +5292,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5447,7 +5335,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5491,7 +5378,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5535,7 +5421,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5579,7 +5464,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5623,7 +5507,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5667,7 +5550,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5711,7 +5593,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5755,7 +5636,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5799,7 +5679,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5843,7 +5722,6 @@
           <t>2026-04-17 12:18:53</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr">
         <is>
           <t>2026-04-17 12:18:53</t>
@@ -5897,8 +5775,6 @@
           <t>Yogesh Bhosale</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>True</t>
@@ -5916,8 +5792,6 @@
           <t>Sidram Battul</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>True</t>
@@ -5935,8 +5809,6 @@
           <t>Sham Kachi</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>True</t>
@@ -5954,8 +5826,6 @@
           <t>sameer shaikh</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>True</t>
@@ -5973,8 +5843,6 @@
           <t>Rajesh chavan</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>True</t>
@@ -5992,8 +5860,6 @@
           <t>Sahil Dighe</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>True</t>
@@ -6011,8 +5877,6 @@
           <t>Gajanan gawande</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>True</t>
@@ -6030,8 +5894,6 @@
           <t>Kiran misal</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>True</t>
@@ -6049,8 +5911,6 @@
           <t>kishor panchal</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>True</t>
@@ -6068,8 +5928,6 @@
           <t>Raju Yadav</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>True</t>
@@ -6087,8 +5945,6 @@
           <t>Lalemashak kunnure</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>True</t>
@@ -6106,8 +5962,6 @@
           <t>Faruk Shaikh</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>True</t>
@@ -6125,8 +5979,6 @@
           <t>Ashraf Momin</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>True</t>
@@ -6144,8 +5996,6 @@
           <t>Abhitabh Gupta</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>True</t>
@@ -6163,8 +6013,6 @@
           <t>Prahalad Yadav</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>True</t>
@@ -6182,8 +6030,6 @@
           <t>Abdul Rehman</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>True</t>
@@ -6201,8 +6047,6 @@
           <t>Ishwar Panchal</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>True</t>
@@ -6220,8 +6064,6 @@
           <t>Nagendra Yadav</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>True</t>
@@ -6239,8 +6081,6 @@
           <t>Pramod Valekar</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>True</t>
@@ -6258,8 +6098,6 @@
           <t>Rahim Dindore</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>True</t>
@@ -6295,6 +6133,236 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>2026-04-17 12:48:07</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Row_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Sr_No</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Engineer_Name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Job_Card_Invoice_No</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Outward_Date</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>TCR_No</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>TCR_Date</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Warranty_Warranty_No</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Bill_Amount</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Incentive</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Ticket_Closed_On_Date</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Part_Name_Part_No</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Material_Description</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>HSN_Code</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>MRP_Product_Price</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>CGST</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>SGST</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U1" s="2" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="V1" s="2" t="inlineStr">
+        <is>
+          <t>Article_No</t>
+        </is>
+      </c>
+      <c r="W1" s="2" t="inlineStr">
+        <is>
+          <t>Part_Sr_No</t>
+        </is>
+      </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t>Money_Received</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Created_At</t>
+        </is>
+      </c>
+      <c r="Z1" s="2" t="inlineStr">
+        <is>
+          <t>Updated_At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>3363e3a3-b674-4ef0-8644-b1848f4d485a</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:11:39</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>TCR-1nan</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>18-Apr-2026</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr"/>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>xsy</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Service work on local purchase - xsy</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:11:39</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-18 17:12:16</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
         <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -79,6 +85,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,19 +489,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xsy</t>
+          <t>panel</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D2" t="n">
-        <v>4000</v>
+        <v>550</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -502,25 +509,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abc</t>
+          <t>climp2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="D3" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -528,189 +535,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>valve</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>600</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>100</v>
-      </c>
-      <c r="D5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>display</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>700</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5700</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>dis</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>100</v>
-      </c>
-      <c r="D7" t="n">
-        <v>400</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>panel</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" t="n">
-        <v>150</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>test 8</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D9" t="n">
-        <v>90</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>test2</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>400</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>OG</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>13</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -724,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J119"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +607,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -790,7 +615,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -804,28 +634,28 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4000</v>
+        <v>550</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-17 12:33:50</t>
+          <t>2026-04-20 12:30:43</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-17 12:33:50</t>
+          <t>2026-04-20 12:30:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -833,7 +663,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -847,28 +682,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4000</v>
+        <v>550</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-17 12:33:58</t>
+          <t>2026-04-20 12:30:48</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-17 12:33:58</t>
+          <t>2026-04-20 12:30:48</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -876,7 +711,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -886,32 +726,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kiran misal</t>
+          <t>Rajesh chavan</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4000</v>
+        <v>550</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-17 12:34:05</t>
+          <t>2026-04-20 12:30:55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-17 12:34:05</t>
+          <t>2026-04-20 12:30:55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -919,37 +759,47 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Sham Kachi</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:59</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:30:59</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -957,7 +807,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -967,27 +822,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiran misal</t>
+          <t>Sidram Battul</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4000</v>
+        <v>550</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-04-17 11:16:50</t>
+          <t>2026-04-20 12:31:04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-17 11:16:50</t>
+          <t>2026-04-20 12:31:04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -995,7 +855,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1005,32 +870,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>sameer shaikh</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4000</v>
+        <v>550</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-04-18 17:11:39</t>
+          <t>2026-04-20 12:31:08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-18 17:11:39</t>
+          <t>2026-04-20 12:31:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1038,7 +903,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1056,19 +926,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1076,7 +946,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1094,19 +969,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1114,37 +989,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sham Kachi</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:17:14</t>
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-17 11:17:14</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1152,7 +1032,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1170,103 +1055,118 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-17 11:02:12</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yogesh Bhosale</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:29:07</t>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-17 11:29:07</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sahil Dighe</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:30:54</t>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-17 11:30:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1284,103 +1184,118 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yogesh Bhosale</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:30:29</t>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-17 11:30:29</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kiran misal</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:31:13</t>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-17 11:31:13</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1398,27 +1313,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1436,27 +1356,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1474,27 +1399,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1512,27 +1442,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cvb</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1550,293 +1485,368 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:26:48</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:29:34</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Sidram Battul</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:41</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:29:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:46</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:29:46</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:51</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:29:51</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:55</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:29:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>sameer shaikh</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:01</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:30:01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Gajanan gawande</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:07</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:30:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1846,159 +1856,189 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yogesh Bhosale</t>
+          <t>Kiran misal</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>880</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-04-17 11:08:57</t>
+          <t>2026-04-20 12:30:11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-04-17 11:08:57</t>
+          <t>2026-04-20 12:30:11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kiran misal</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:30:15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kiran misal</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:18</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-17 11:07:54</t>
+          <t>2026-04-20 12:30:18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TI-123</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Kiran misal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-04-17 11:28:54</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:20</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-04-17 11:28:54</t>
+          <t>2026-04-20 12:30:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>TI-123</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2016,12 +2056,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-04-17 11:29:02</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-04-17 11:29:02</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2032,39 +2072,39 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nagendra Yadav</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:34:48</t>
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-04-17 11:34:48</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2075,16 +2115,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2102,12 +2142,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2158,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2145,12 +2185,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2161,16 +2201,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2188,12 +2228,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2204,16 +2244,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2231,12 +2271,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2247,16 +2287,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2274,12 +2314,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2290,16 +2330,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2317,12 +2357,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2333,16 +2373,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2360,12 +2400,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2376,16 +2416,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2403,12 +2443,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2419,16 +2459,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2446,12 +2486,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2462,16 +2502,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2489,12 +2529,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2505,16 +2545,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2532,12 +2572,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2548,16 +2588,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2575,12 +2615,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2591,16 +2631,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2618,12 +2658,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2634,16 +2674,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2661,12 +2701,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2677,16 +2717,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2704,12 +2744,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2720,16 +2760,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2747,12 +2787,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2763,16 +2803,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2790,12 +2830,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2806,16 +2846,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2833,12 +2873,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2849,16 +2889,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2876,12 +2916,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2892,16 +2932,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2919,12 +2959,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2935,16 +2975,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2962,12 +3002,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -2978,16 +3018,16 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3005,12 +3045,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3021,16 +3061,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3048,12 +3088,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3064,16 +3104,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3091,12 +3131,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3107,16 +3147,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3134,12 +3174,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3150,16 +3190,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3177,12 +3217,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3193,16 +3233,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3220,12 +3260,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3236,16 +3276,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3263,12 +3303,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3319,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3306,12 +3346,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3322,16 +3362,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3349,12 +3389,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3365,16 +3405,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3392,12 +3432,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3408,16 +3448,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3435,12 +3475,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3451,16 +3491,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3478,12 +3518,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3494,16 +3534,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3521,12 +3561,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3537,16 +3577,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3564,12 +3604,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3580,16 +3620,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3607,12 +3647,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3623,16 +3663,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3650,12 +3690,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3666,16 +3706,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3693,12 +3733,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -3709,16 +3749,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>vss101</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3736,75 +3776,75 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-04-17 11:33:16</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>vss102</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Abhitabh Gupta</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>300</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:54:08</t>
+        <v>0</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-04-17 11:54:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3822,32 +3862,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3865,32 +3905,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3908,32 +3948,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3951,32 +3991,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3994,32 +4034,32 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4037,32 +4077,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4080,32 +4120,32 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>vss104</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4123,75 +4163,75 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-04-17 11:43:33</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kiran misal</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>400</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:52:49</t>
+        <v>0</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-04-17 11:52:49</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4209,32 +4249,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4252,75 +4292,75 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>kishor panchal</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>400</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:52:36</t>
+        <v>0</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-04-17 11:52:36</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4338,32 +4378,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4381,75 +4421,75 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Faruk Shaikh</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>400</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-04-17 11:52:07</t>
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-04-17 11:52:07</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4467,32 +4507,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4510,32 +4550,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>vss105</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4553,32 +4593,32 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-04-17 11:51:08</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4596,32 +4636,32 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4639,32 +4679,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4682,32 +4722,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4725,32 +4765,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4768,32 +4808,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4811,32 +4851,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4854,32 +4894,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4897,32 +4937,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4940,32 +4980,32 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4983,32 +5023,32 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5026,32 +5066,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>vss108</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5069,32 +5109,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-04-17 12:13:30</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5112,123 +5152,118 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lalemashak kunnure</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-04-17 12:46:22</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-04-17 12:46:22</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OUT</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sidram Battul</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3500</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-04-17 12:19:55</t>
+        <v>0</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-04-17 12:19:55</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5246,32 +5281,32 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -5289,32 +5324,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5332,32 +5367,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5375,32 +5410,32 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5418,32 +5453,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5461,32 +5496,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5504,32 +5539,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5547,32 +5582,32 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5590,32 +5625,32 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5633,32 +5668,32 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5676,32 +5711,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>vss109</t>
+          <t>fghj</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -5719,12 +5754,2248 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>2026-04-17 12:18:53</t>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>99</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>100</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>101</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>102</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>103</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>104</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>105</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>106</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>107</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>108</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>109</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>110</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>111</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>112</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>113</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>114</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>115</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>116</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>117</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>118</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>119</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>120</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>121</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>122</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>123</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>124</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>125</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>126</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>127</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>128</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>129</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>130</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>131</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>132</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>133</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>134</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>135</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>136</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>137</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>138</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>139</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>140</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>141</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>142</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>143</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>144</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>145</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>146</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>147</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>148</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>149</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>150</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:28:58</t>
         </is>
       </c>
     </row>
@@ -5739,7 +8010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5782,7 +8053,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5799,7 +8070,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5816,7 +8087,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5833,7 +8104,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5850,7 +8121,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5867,7 +8138,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5884,7 +8155,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5901,7 +8172,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5918,7 +8189,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5935,7 +8206,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5952,7 +8223,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5969,7 +8240,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -5986,7 +8257,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6003,7 +8274,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6020,7 +8291,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6037,7 +8308,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6054,7 +8325,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6071,7 +8342,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6088,7 +8359,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6105,34 +8376,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-04-17 12:47:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>5757</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2026-04-17 12:48:07</t>
+          <t>2026-04-20 12:20:22</t>
         </is>
       </c>
     </row>
@@ -6147,7 +8391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6285,7 +8529,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>3363e3a3-b674-4ef0-8644-b1848f4d485a</t>
+          <t>c63e199e-7d5f-48f8-8978-440933a4e639</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -6293,46 +8537,38 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr"/>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18 17:11:39</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>TCR-1nan</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>18-Apr-2026</t>
-        </is>
-      </c>
+          <t>2026-04-20 12:29:34</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
       <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18</t>
-        </is>
-      </c>
+      <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>xsy</t>
+          <t>climp2</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>Service work on local purchase - xsy</t>
+          <t>Service work on 🏪 local purchase - climp2</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -6342,27 +8578,1291 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="W2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:34</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2b755971-285a-49db-8e95-6ad8aaf7de59</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:41</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:41</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>08a43173-03ee-494a-b01b-b2358ea098ef</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:46</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:46</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2612db6c-dd7c-4608-8335-8194eed99933</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:51</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:51</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>f1eb1c5e-6e4d-44c8-82d2-dd4bee0f75a7</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Yogesh Bhosale</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:55</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>TCR-5nan</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:29:55</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:33:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>d874b855-c024-4b94-b1b5-05b3feaf38d0</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="X2" s="3" t="b">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>sameer shaikh</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:01</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr"/>
+      <c r="V7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:01</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>8438c130-7db8-42a3-9db3-bec6639e83a1</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:07</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr"/>
+      <c r="V8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:08</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>fa7a7b20-c718-48ec-9f4f-62d8a5c012c7</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:11</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr"/>
+      <c r="V9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:11</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>478242fe-8a92-44a9-b62d-e5beb13b00ed</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:15</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>TCR-9nan</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18 17:11:39</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18 17:12:16</t>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:15</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:33:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>6c10ed03-615d-4757-8991-7d196bee9a3e</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:18</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:18</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>81835d75-5dce-44b8-9dca-e7a588684b39</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:20</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:20</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>8f759407-fe3b-4b10-aa58-5465c0cb28c6</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>cvb</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:43</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>TCR-12nan</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:43</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:32:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>19d2ed20-15b2-4d4d-b787-1da7e7251b53</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>vb567</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:48</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>TCR-13nan</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr"/>
+      <c r="Q14" s="4" t="inlineStr"/>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:48</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:32:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>466d0c7b-c48e-468f-9872-42b4ca9ab3e6</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh chavan</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>cvb</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:55</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:55</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>730f7839-45c9-4d4a-8a7a-736dbca5e0ad</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sham Kachi</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>cvb</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr"/>
+      <c r="V16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:59</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:30:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>5795cc7c-ec9c-45fd-a88d-93221b8d4387</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>cvb</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:04</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr"/>
+      <c r="V17" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:04</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>71a05cac-4701-485d-9c97-7d986764289d</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>sameer shaikh</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>cvb</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:08</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - panel</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:09</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:31:09</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -7977,25 +7977,30 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Sidram Battul</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
           <t>2026-04-20 12:28:58</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:44:07</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>2026-04-20 12:28:58</t>
+          <t>2026-04-20 13:44:07</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9866,6 +9871,82 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4306fdf7-23c0-4509-b157-e0177fc5f586</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>fghj</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:44:07</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>climp2</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - climp2</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="X19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:44:07</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 13:44:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -47,14 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -2053,12 +2053,24 @@
           <t>2026-04-20 15:15:36</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>TCR-nan</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>21-Apr-2026</t>
+        </is>
+      </c>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
           <t>xz</t>
@@ -2076,7 +2088,7 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
@@ -2087,257 +2099,257 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:36</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21 11:52:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>42fdc5e7-d5ae-468f-b960-81f65bd1f3d9</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>sdfg</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:41</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - xz</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
+      <c r="Q3" s="4" t="inlineStr"/>
+      <c r="R3" s="4" t="inlineStr"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr"/>
+      <c r="U3" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:36</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>42fdc5e7-d5ae-468f-b960-81f65bd1f3d9</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:41</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>40918705-5523-4efa-9d8b-2e7c8b561d0b</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>vishal</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>sdfg</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:45</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>TCR-3nan</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>xz</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Service work on 🏢 company purchase - xz</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="n">
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>40918705-5523-4efa-9d8b-2e7c8b561d0b</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="V4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:45</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>ef2a0047-8c8e-4c16-abb8-2b8e2fe68cb6</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>vishal</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>sdfg</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>TCR-3nan</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:49</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>TCR-4nan</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>20-Apr-2026</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>xz</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Service work on 🏢 company purchase - xz</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" s="4" t="b">
+      <c r="V5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:16:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ef2a0047-8c8e-4c16-abb8-2b8e2fe68cb6</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>sdfg</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>2026-04-20 15:15:49</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>TCR-4nan</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Service work on 🏢 company purchase - xz</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="W5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:49</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>2026-04-20 15:16:20</t>
         </is>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -47,14 +51,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -86,6 +90,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -453,34 +463,42 @@
   </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Part_Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>CP</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Stock_Level</t>
         </is>
@@ -525,54 +543,66 @@
   </sheetPr>
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Sr_No</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Purchase_Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Tax_Invoice_No</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Charges</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>In_Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>Out_Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -1469,41 +1499,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Engineer_Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>BP_ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>PPRR_ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Created_At</t>
         </is>
@@ -1877,12 +1916,39 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>shubham</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>wf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:16</t>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-04-21 17:05:44</t>
         </is>
       </c>
     </row>
@@ -1899,129 +1965,156 @@
   </sheetPr>
   <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="19" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Row_ID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Engineer_Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Job_Card_Invoice_No</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Outward_Date</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>TCR_No</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>TCR_Date</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Warranty_Warranty_No</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Bill_Amount</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Ticket_Closed_On_Date</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Part_Name_Part_No</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Material_Description</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>HSN_Code</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>MRP_Product_Price</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>CGST</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="6" t="inlineStr">
         <is>
           <t>SGST</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="6" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="6" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="6" t="inlineStr">
         <is>
           <t>Part_Sr_No</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="6" t="inlineStr">
         <is>
           <t>Money_Received</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="6" t="inlineStr">
         <is>
           <t>Created_At</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>Updated_At</t>
         </is>
@@ -2088,7 +2181,7 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
@@ -2099,257 +2192,257 @@
         <v>1</v>
       </c>
       <c r="W2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:36</t>
+        </is>
+      </c>
+      <c r="Y2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21 17:07:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>42fdc5e7-d5ae-468f-b960-81f65bd1f3d9</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>sdfg</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:41</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - xz</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:41</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-21 17:07:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>40918705-5523-4efa-9d8b-2e7c8b561d0b</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>vishal</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>sdfg</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:45</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>TCR-3nan</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - xz</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
+      <c r="Q4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr"/>
+      <c r="U4" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:36</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-21 11:52:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>42fdc5e7-d5ae-468f-b960-81f65bd1f3d9</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:45</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>ef2a0047-8c8e-4c16-abb8-2b8e2fe68cb6</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>vishal</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>sdfg</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20 15:15:49</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>TCR-4nan</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>20-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>xz</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Service work on 🏢 company purchase - xz</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr"/>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
+      <c r="Q5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="V3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>40918705-5523-4efa-9d8b-2e7c8b561d0b</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>sdfg</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>TCR-3nan</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>Service work on 🏢 company purchase - xz</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" s="3" t="b">
+      <c r="V5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:16:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ef2a0047-8c8e-4c16-abb8-2b8e2fe68cb6</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>sdfg</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>2026-04-20 15:15:49</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>TCR-4nan</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Service work on 🏢 company purchase - xz</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:49</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>2026-04-20 15:16:20</t>
         </is>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,10 +30,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -80,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -90,12 +86,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,44 +451,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Part_Name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>CP</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Stock_Level</t>
         </is>
@@ -512,14 +494,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -527,7 +509,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -541,68 +601,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Sr_No</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Purchase_Type</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tax_Invoice_No</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Engineer</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Charges</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>In_Date</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Out_Date</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -624,7 +672,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -634,25 +682,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:36</t>
+          <t>2026-04-22 16:52:32</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:36</t>
+          <t>2026-04-22 16:52:32</t>
         </is>
       </c>
     </row>
@@ -672,7 +720,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -682,25 +730,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:41</t>
+          <t>2026-04-22 16:52:42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:41</t>
+          <t>2026-04-22 16:52:42</t>
         </is>
       </c>
     </row>
@@ -720,7 +768,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -730,25 +778,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Sidram Battul</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:45</t>
+          <t>2026-04-22 16:52:47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:45</t>
+          <t>2026-04-22 16:52:47</t>
         </is>
       </c>
     </row>
@@ -768,7 +816,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -778,25 +826,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Rajesh chavan</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:49</t>
+          <t>2026-04-22 16:52:52</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:49</t>
+          <t>2026-04-22 16:52:52</t>
         </is>
       </c>
     </row>
@@ -816,7 +864,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -834,12 +882,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
@@ -859,7 +907,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -877,12 +925,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
@@ -902,7 +950,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +968,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
@@ -945,7 +993,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -963,12 +1011,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
@@ -988,7 +1036,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1006,12 +1054,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1079,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1049,32 +1097,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:51:58</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1092,32 +1140,32 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1135,32 +1183,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1178,75 +1226,80 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OUT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Prahalad Yadav</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:07:06</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 17:07:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,32 +1317,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1307,32 +1360,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1350,32 +1403,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1393,32 +1446,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>🏢 Company</t>
+          <t>🏪 Local</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss102</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1436,55 +1489,1782 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-20 15:14:24</t>
+          <t>2026-04-22 16:56:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>10</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>16</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>17</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>18</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>19</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>20</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>21</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:07</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>22</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:01</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:55</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>24</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:48</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>25</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:37</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>🏢 Company</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>sdfg</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ishwar Panchal</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:31</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Prahalad Yadav</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:37</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Store</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:14:24</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:14:24</t>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rahim Dindore</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:07</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pramod Valekar</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:11</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pramod Valekar</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>14000</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>8</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>9</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>11</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>12</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>13</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>14</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>🏪 Local</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:05:29</t>
         </is>
       </c>
     </row>
@@ -1499,50 +3279,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Engineer_Name</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>BP_ID</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>PPRR_ID</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Created_At</t>
         </is>
@@ -1561,7 +3332,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1578,7 +3349,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1595,7 +3366,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1612,7 +3383,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1629,7 +3400,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1646,7 +3417,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1663,7 +3434,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1680,7 +3451,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1697,7 +3468,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1714,7 +3485,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1731,7 +3502,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1748,7 +3519,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1765,7 +3536,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1782,7 +3553,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1799,7 +3570,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1816,7 +3587,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1833,7 +3604,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1850,7 +3621,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1867,7 +3638,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1884,71 +3655,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-04-20 15:13:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fd</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>bv</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>vishalshinde4511@gmail.com</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>9022808423</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>shubham</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>wf</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>g</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-04-21 17:05:44</t>
+          <t>2026-04-22 16:50:17</t>
         </is>
       </c>
     </row>
@@ -1963,158 +3670,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="19" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Row_ID</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Engineer_Name</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Job_Card_Invoice_No</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Outward_Date</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>TCR_No</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>TCR_Date</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Warranty_Warranty_No</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Bill_Amount</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Incentive</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Ticket_Closed_On_Date</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Part_Name_Part_No</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Material_Description</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>HSN_Code</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>MRP_Product_Price</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>CGST</t>
         </is>
       </c>
-      <c r="R1" s="6" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>SGST</t>
         </is>
       </c>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="U1" s="6" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Article_No</t>
         </is>
       </c>
-      <c r="V1" s="6" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Part_Sr_No</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Money_Received</t>
         </is>
       </c>
-      <c r="X1" s="6" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Created_At</t>
         </is>
       </c>
-      <c r="Y1" s="6" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Updated_At</t>
         </is>
@@ -2123,55 +3803,43 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>78d3afed-2765-4628-8c58-25c2238d6180</t>
+          <t>be50660a-b93b-473b-8f16-929316b0d75b</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:36</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>TCR-nan</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>21-Apr-2026</t>
-        </is>
-      </c>
+          <t>2026-04-22 16:52:32</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
       <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
+      <c r="K2" s="3" t="inlineStr"/>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Service work on 🏢 company purchase - xz</t>
+          <t>Service work on 🏢 company purchase - lamp</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr"/>
@@ -2181,7 +3849,7 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>COMPLETED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
@@ -2196,39 +3864,39 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:36</t>
+          <t>2026-04-22 16:52:32</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21 17:07:46</t>
+          <t>2026-04-22 16:52:32</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>42fdc5e7-d5ae-468f-b960-81f65bd1f3d9</t>
+          <t>ac9e1654-d9de-4831-a1b3-d32938894d24</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Yogesh Bhosale</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:41</t>
+          <t>2026-04-22 16:52:42</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
@@ -2239,12 +3907,12 @@
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Service work on 🏢 company purchase - xz</t>
+          <t>Service work on 🏢 company purchase - lamp</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
@@ -2269,152 +3937,148 @@
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:41</t>
+          <t>2026-04-22 16:52:42</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21 17:07:36</t>
+          <t>2026-04-22 16:52:42</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>40918705-5523-4efa-9d8b-2e7c8b561d0b</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>vishal</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>sdfg</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>TCR-3nan</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr"/>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>Service work on 🏢 company purchase - xz</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr"/>
-      <c r="O4" s="4" t="inlineStr"/>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2bfcd730-e4d0-4f99-a453-48820d425ff7</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>vss101</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:52:47</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - lamp</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="W4" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:15:45</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-20 15:16:35</t>
+      <c r="W4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:52:47</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:52:47</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>ef2a0047-8c8e-4c16-abb8-2b8e2fe68cb6</t>
+          <t>e680921f-0081-4445-8a67-d95a2f8c3673</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>vishal</t>
+          <t>Rajesh chavan</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>sdfg</t>
+          <t>vss101</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:49</t>
+          <t>2026-04-22 16:52:52</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>TCR-4nan</t>
+          <t>TCR-nan</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>w234</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>100</v>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>lamp</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>Service work on 🏢 company purchase - xz</t>
+          <t>Service work on 🏢 company purchase - lamp</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr"/>
@@ -2439,12 +4103,883 @@
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:15:49</t>
+          <t>2026-04-22 16:52:52</t>
         </is>
       </c>
       <c r="Y5" s="4" t="inlineStr">
         <is>
-          <t>2026-04-20 15:16:20</t>
+          <t>2026-04-22 16:54:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>54f8b677-02f1-4abb-bd3e-e5a3e5628028</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:37</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:37</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>c6416092-685a-4c61-b714-439cda12d3e7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Gajanan gawande</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:48</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="W7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:48</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>5d91c1c6-f349-400e-aaf8-e7ba065f0adc</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:55</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>TCR-6622</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr"/>
+      <c r="U8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="W8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:56:55</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:07:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>942a8f29-d40c-4b9f-97e1-71003cbabe42</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:01</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>TCR-6623</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>w2093</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr"/>
+      <c r="U9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:01</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:08:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>f9f6c340-e762-4c57-96f8-0eb4d473d44d</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Kiran misal</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:07</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>TCR-6612</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr"/>
+      <c r="Q10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr"/>
+      <c r="U10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="W10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 16:57:07</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:09:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>78814050-1a48-4e06-91ae-f2b9530daa55</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Rahim Dindore</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:07</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - panel</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:07</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>5df3c57e-fde0-4d32-b579-37187be95294</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Pramod Valekar</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:11</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - panel</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:11</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>db187d75-4913-4dfd-9271-08c179c17e32</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Pramod Valekar</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>vss104</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:15</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>TCR-6644</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>22-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - panel</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr"/>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:15</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:09:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>e46ca377-51a2-4fc0-8df5-4440662fb388</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Ishwar Panchal</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:31</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - remote</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:32</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>6eae1327-5cf4-4dcf-9fda-2f0637ca40fe</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Prahalad Yadav</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:37</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>remote</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - remote</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:37</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:06:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>b10353f2-6ea9-4c5e-827b-0843185ad19b</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Prahalad Yadav</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>vss102</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:07:06</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>wire</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Service work on 🏪 local purchase - wire</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:07:06</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-22 17:07:06</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3265,6 +3265,92 @@
       <c r="J60" t="inlineStr">
         <is>
           <t>2026-04-22 17:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>26</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:39:35</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:39:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>27</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>vss103</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:39:35</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-04-23 11:39:35</t>
         </is>
       </c>
     </row>

--- a/resQ_Enterprise_Inventory.xlsx
+++ b/resQ_Enterprise_Inventory.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,32 @@
       </c>
       <c r="F5" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>400</v>
+      </c>
+      <c r="D6" t="n">
+        <v>800</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OG</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3351,6 +3377,441 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>2026-04-23 11:39:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>800</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:46:20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:46:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>8</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>9</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>🏢 Company</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:45:10</t>
         </is>
       </c>
     </row>
@@ -3756,7 +4217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4616,75 +5077,87 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>78814050-1a48-4e06-91ae-f2b9530daa55</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Rahim Dindore</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>vss104</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-04-22 17:06:07</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>TCR-nan</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>29-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>panel</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>Service work on 🏪 local purchase - panel</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="n">
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="W11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
         <is>
           <t>2026-04-22 17:06:07</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-22 17:06:07</t>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 16:31:04</t>
         </is>
       </c>
     </row>
@@ -5069,6 +5542,95 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>90c41c44-8837-464a-bcf9-6c1317485127</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Sidram Battul</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>vss108</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:46:20</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>TCR-6326</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>29-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Service work on 🏢 company purchase - abc</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="n">
+        <v>401</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:46:20</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-29 17:47:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
